--- a/extdata/test_rolling_hours_result.xlsx
+++ b/extdata/test_rolling_hours_result.xlsx
@@ -365,10 +365,10 @@
         <v>2024</v>
       </c>
       <c r="B2" t="n">
-        <v>2808</v>
+        <v>1056</v>
       </c>
       <c r="C2" t="n">
-        <v>117</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
